--- a/Data Exploration 1st Assignment.xlsx
+++ b/Data Exploration 1st Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a96f77e54b877ef/Data Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{CC4547FE-17B9-4447-AAC3-C4423E3BBF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4ED93A4-6C04-4E72-AF87-4F4ADB8EE531}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{CC4547FE-17B9-4447-AAC3-C4423E3BBF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894E3469-3CE5-4BCC-8C99-CD0E419E223A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A59290A1-6974-4F63-AD7C-E6D4EFFA81B5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A59290A1-6974-4F63-AD7C-E6D4EFFA81B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1334,7 +1333,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>61</v>
       </c>
@@ -1382,7 +1381,7 @@
         <v>High Price</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
@@ -1430,7 +1429,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
@@ -1478,7 +1477,7 @@
         <v>High Price</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>75</v>
       </c>
@@ -1502,7 +1501,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>77</v>
       </c>
@@ -1526,7 +1525,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>48</v>
       </c>
@@ -1550,7 +1549,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>79</v>
       </c>
@@ -1574,7 +1573,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>82</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -1622,7 +1621,7 @@
         <v>standard Price</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>87</v>
       </c>
@@ -1670,7 +1669,7 @@
         <v>High Price</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -1767,8 +1766,8 @@
         <v>US</v>
       </c>
       <c r="I2" s="6" t="str">
-        <f>MID(A2,4,6)</f>
-        <v>JAN-US</v>
+        <f>MID(A2,4,3)</f>
+        <v>JAN</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1799,8 +1798,8 @@
         <v>US</v>
       </c>
       <c r="I3" s="6" t="str">
-        <f>MID(A3,4,6)</f>
-        <v>FEB-US</v>
+        <f t="shared" ref="I3:I35" si="2">MID(A3,4,3)</f>
+        <v>FEB</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1831,8 +1830,8 @@
         <v>US</v>
       </c>
       <c r="I4" s="6" t="str">
-        <f t="shared" ref="I4:I35" si="2">MID(A4,4,6)</f>
-        <v>MAR-US</v>
+        <f t="shared" si="2"/>
+        <v>MAR</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1864,7 +1863,7 @@
       </c>
       <c r="I5" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>APR-US</v>
+        <v>APR</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1896,7 +1895,7 @@
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>MAY-US</v>
+        <v>MAY</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1928,7 +1927,7 @@
       </c>
       <c r="I7" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUN-UK</v>
+        <v>JUN</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1960,7 +1959,7 @@
       </c>
       <c r="I8" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUL-UK</v>
+        <v>JUL</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -1992,7 +1991,7 @@
       </c>
       <c r="I9" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>AUG-UK</v>
+        <v>AUG</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2024,7 +2023,7 @@
       </c>
       <c r="I10" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>SEP-UK</v>
+        <v>SEP</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2056,7 +2055,7 @@
       </c>
       <c r="I11" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>OCT-UK</v>
+        <v>OCT</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2088,10 +2087,10 @@
       </c>
       <c r="I12" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUN-IN</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>42</v>
       </c>
@@ -2120,7 +2119,7 @@
       </c>
       <c r="I13" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>NOV-AU</v>
+        <v>NOV</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2152,10 +2151,10 @@
       </c>
       <c r="I14" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>DEC-DE</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -2184,10 +2183,10 @@
       </c>
       <c r="I15" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>FEB-CA</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>FEB</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
@@ -2216,7 +2215,7 @@
       </c>
       <c r="I16" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>APR-ES</v>
+        <v>APR</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2248,10 +2247,10 @@
       </c>
       <c r="I17" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>AUG-CA</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
@@ -2280,10 +2279,10 @@
       </c>
       <c r="I18" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>AUG-CN</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
@@ -2312,10 +2311,10 @@
       </c>
       <c r="I19" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JAN-IT</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JAN</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2344,10 +2343,10 @@
       </c>
       <c r="I20" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>MAR-UK</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>MAR</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>61</v>
       </c>
@@ -2376,10 +2375,10 @@
       </c>
       <c r="I21" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>AUG-US</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>64</v>
       </c>
@@ -2408,7 +2407,7 @@
       </c>
       <c r="I22" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>MAY-RU</v>
+        <v>MAY</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2440,10 +2439,10 @@
       </c>
       <c r="I23" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JAN-CA</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JAN</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
@@ -2472,7 +2471,7 @@
       </c>
       <c r="I24" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUL-BR</v>
+        <v>JUL</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="26" x14ac:dyDescent="0.35">
@@ -2504,10 +2503,10 @@
       </c>
       <c r="I25" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>AUG-CA</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>73</v>
       </c>
@@ -2536,10 +2535,10 @@
       </c>
       <c r="I26" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>SEP-CA</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>SEP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>75</v>
       </c>
@@ -2568,10 +2567,10 @@
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUN-CA</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>77</v>
       </c>
@@ -2600,10 +2599,10 @@
       </c>
       <c r="I28" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUL-CA</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JUL</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>48</v>
       </c>
@@ -2632,10 +2631,10 @@
       </c>
       <c r="I29" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>APR-ES</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>79</v>
       </c>
@@ -2664,10 +2663,10 @@
       </c>
       <c r="I30" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>MAR-CA</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>MAR</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>82</v>
       </c>
@@ -2696,10 +2695,10 @@
       </c>
       <c r="I31" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>APR-CA</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
@@ -2728,10 +2727,10 @@
       </c>
       <c r="I32" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>MAY-CA</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>MAY</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>87</v>
       </c>
@@ -2760,10 +2759,10 @@
       </c>
       <c r="I33" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>DEC-CA</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -2792,10 +2791,10 @@
       </c>
       <c r="I34" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUN-IN</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -2824,7 +2823,7 @@
       </c>
       <c r="I35" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>JUL-FR</v>
+        <v>JUL</v>
       </c>
     </row>
   </sheetData>
